--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,14 +462,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.07980125885594425</v>
+        <v>-0.059953273309308</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2731890688710343</v>
+        <v>0.1799340235459657</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.3993065320892725</v>
+        <v>-0.3811982244164103</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.5674970284670116</v>
+        <v>-0.5178302619018619</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2173639328074389</v>
+        <v>0.1524908295719816</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.4169803382752419</v>
+        <v>-0.4425253155143519</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>33.19940327166113</v>
+        <v>40.54477968920433</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2942557325876809</v>
+        <v>-0.0457921273157228</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2315911812966207</v>
+        <v>0.2933207928559029</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.514481034892746</v>
+        <v>-0.07151517863797147</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.967554110737273</v>
+        <v>-0.1038763645556365</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3216284580214734</v>
+        <v>0.1865281638259723</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9462666094227976</v>
+        <v>-0.2553961426238249</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>41.95100671378169</v>
+        <v>24.83907775643644</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.08968638977678822</v>
+        <v>-0.1058225600709961</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2107529707565552</v>
+        <v>0.2188522220852839</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.4300838996697643</v>
+        <v>-0.4908526588619582</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.6196164236468259</v>
+        <v>-0.6624252840686254</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2358608563296047</v>
+        <v>0.2636537514761027</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.3952083949786734</v>
+        <v>-0.417008524759008</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>44.87724921526034</v>
+        <v>61.5006966291019</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.09558866605968741</v>
+        <v>-0.09754420316055357</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2110803791455298</v>
+        <v>0.2416148709220763</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.4844487256333346</v>
+        <v>-0.3834193219040517</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.7345914587592077</v>
+        <v>-0.5275696697407007</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1242952573676818</v>
+        <v>0.2229049560131501</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.8023593193670866</v>
+        <v>-0.4547388301005715</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>42.75204113958401</v>
+        <v>46.09324033928419</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.1571412745473026</v>
+        <v>0.2765127199618982</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2423980902043612</v>
+        <v>0.2618752428871977</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.6848093587868067</v>
+        <v>1.041594838283688</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.9457553552882725</v>
+        <v>1.48539894634953</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2028519259689103</v>
+        <v>0.162103967085905</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8055792974460377</v>
+        <v>1.777298816819824</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>53.29943825235043</v>
+        <v>52.11747964581281</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.2209661528921998</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3659366432237393</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1.130587715057698</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1.680415046359108</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1298634346606894</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>3.35826084398044</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>41.47407913594768</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>